--- a/Session 3/Pivots.xlsx
+++ b/Session 3/Pivots.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b2wcompletetraining057-my.sharepoint.com/personal/michael_chittenden_justit_co_uk/Documents/Scenario-Demonstration-Training/Session 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FAE4352-DEA7-40E1-9375-6F40D6449B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{6FAE4352-DEA7-40E1-9375-6F40D6449B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18E02214-E1A7-4A6B-87B7-5E1EB5846818}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9BB4D2A1-FDFC-4D4B-95EB-21AD45D4BCEB}"/>
+    <workbookView minimized="1" xWindow="25245" yWindow="3405" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9BB4D2A1-FDFC-4D4B-95EB-21AD45D4BCEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Level 1" sheetId="9" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="15" r:id="rId2"/>
-    <sheet name="Level 2" sheetId="13" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="12" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="17" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="16" r:id="rId4"/>
+    <sheet name="Level 2" sheetId="13" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId6"/>
+    <pivotCache cacheId="6" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -63,7 +65,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -85,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="168">
   <si>
     <t>PT1001</t>
   </si>
@@ -520,6 +522,75 @@
   </si>
   <si>
     <t>Calculated Age2</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Appt</t>
+  </si>
+  <si>
+    <t>Average of Appts</t>
+  </si>
+  <si>
+    <t>Max of Appt Count</t>
+  </si>
+  <si>
+    <t>Min of Appt Counts</t>
+  </si>
+  <si>
+    <t>StdDev of Appt Count</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Total Sum of Appt</t>
+  </si>
+  <si>
+    <t>Total Average of Appts</t>
+  </si>
+  <si>
+    <t>Total Max of Appt Count</t>
+  </si>
+  <si>
+    <t>Total Min of Appt Counts</t>
+  </si>
+  <si>
+    <t>Total StdDev of Appt Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table </t>
+  </si>
+  <si>
+    <t>Comp A</t>
+  </si>
+  <si>
+    <t>Comp B</t>
+  </si>
+  <si>
+    <t>Tier 1 SLA</t>
+  </si>
+  <si>
+    <t>Tier 2 SlA</t>
+  </si>
+  <si>
+    <t>Tier 1</t>
+  </si>
+  <si>
+    <t>Tier 2</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max </t>
   </si>
 </sst>
 </file>
@@ -673,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -696,9 +767,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -708,6 +776,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,10 +855,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Michael Chittenden" refreshedDate="46013.379396875003" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="35" xr:uid="{61114D7F-0937-4A7A-BF43-1F1D37EA4D59}">
   <cacheSource type="worksheet">
@@ -848,7 +920,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
     </cacheField>
     <cacheField name="DNA" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="No"/>
+        <s v="Yes"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Dept" numFmtId="0">
       <sharedItems/>
@@ -857,7 +932,20 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2025" maxValue="2025"/>
     </cacheField>
     <cacheField name="Month" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12" count="12">
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="1"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Outcome" numFmtId="0">
       <sharedItems/>
@@ -872,7 +960,11 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Follow Up action" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="NO action required"/>
+        <s v="Escalate"/>
+        <s v="Reminder"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -899,14 +991,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="2"/>
     <s v="Ongoing"/>
     <x v="0"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1002"/>
@@ -922,14 +1014,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="3"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1003"/>
@@ -945,14 +1037,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="4"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1004"/>
@@ -968,14 +1060,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="5"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1005"/>
@@ -991,14 +1083,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="6"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1006"/>
@@ -1014,14 +1106,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="7"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1007"/>
@@ -1037,14 +1129,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="3"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="8"/>
     <s v="Improved"/>
     <x v="0"/>
     <s v="Has Missed Appointment"/>
-    <s v="Escalate"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="PT1008"/>
@@ -1060,14 +1152,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="9"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1009"/>
@@ -1083,14 +1175,14 @@
     <x v="1"/>
     <x v="1"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="10"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1010"/>
@@ -1106,14 +1198,14 @@
     <x v="1"/>
     <x v="1"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="11"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1011"/>
@@ -1129,14 +1221,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="12"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1012"/>
@@ -1152,14 +1244,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="1"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1013"/>
@@ -1175,14 +1267,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="2"/>
     <s v="Ongoing"/>
     <x v="0"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1014"/>
@@ -1198,14 +1290,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="5"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="3"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Missed Appointment"/>
-    <s v="Escalate"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="PT1015"/>
@@ -1221,14 +1313,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="4"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1016"/>
@@ -1244,14 +1336,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="5"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1017"/>
@@ -1267,14 +1359,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="6"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1018"/>
@@ -1290,14 +1382,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="7"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1019"/>
@@ -1313,14 +1405,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="8"/>
     <s v="Improved"/>
     <x v="0"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1020"/>
@@ -1336,14 +1428,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="9"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1021"/>
@@ -1359,14 +1451,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="10"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Missed Appointment"/>
-    <s v="Reminder"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="PT1022"/>
@@ -1382,14 +1474,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="11"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1023"/>
@@ -1405,14 +1497,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="12"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1024"/>
@@ -1428,14 +1520,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="1"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1025"/>
@@ -1451,14 +1543,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="2"/>
     <s v="Ongoing"/>
     <x v="0"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1026"/>
@@ -1474,14 +1566,14 @@
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="3"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1027"/>
@@ -1497,14 +1589,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="4"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1028"/>
@@ -1520,14 +1612,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="4"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="5"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Missed Appointment"/>
-    <s v="Escalate"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="PT1029"/>
@@ -1543,14 +1635,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="6"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1030"/>
@@ -1566,14 +1658,14 @@
     <x v="1"/>
     <x v="1"/>
     <n v="1"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="7"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1031"/>
@@ -1589,14 +1681,14 @@
     <x v="0"/>
     <x v="1"/>
     <n v="2"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="8"/>
     <s v="Improved"/>
     <x v="0"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1032"/>
@@ -1612,14 +1704,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="3"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="9"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1033"/>
@@ -1635,14 +1727,14 @@
     <x v="1"/>
     <x v="1"/>
     <n v="4"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="10"/>
     <s v="Ongoing"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1034"/>
@@ -1658,14 +1750,14 @@
     <x v="1"/>
     <x v="0"/>
     <n v="5"/>
-    <s v="No"/>
+    <x v="0"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="11"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Not Missed Appointment"/>
-    <s v="NO action required"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="PT1035"/>
@@ -1681,33 +1773,47 @@
     <x v="1"/>
     <x v="1"/>
     <n v="1"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <s v="Cardiology"/>
     <n v="2025"/>
     <n v="12"/>
     <s v="Improved"/>
     <x v="1"/>
     <s v="Has Missed Appointment"/>
-    <s v="Reminder"/>
+    <x v="2"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5385CB7-A159-4308-91FA-37B7D3B087D4}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5385CB7-A159-4308-91FA-37B7D3B087D4}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="3">
         <item h="1" x="0"/>
@@ -1723,8 +1829,166 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6745C57C-65AE-4BA0-BACC-758D93A0E433}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B4:Q9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="21">
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="-2"/>
+    <field x="10"/>
+  </colFields>
+  <colItems count="15">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1" i="2">
+      <x v="1"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+      <x/>
+    </i>
+    <i r="1" i="3">
+      <x v="1"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+      <x/>
+    </i>
+    <i r="1" i="4">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+    <i t="grand" i="1">
+      <x/>
+    </i>
+    <i t="grand" i="2">
+      <x/>
+    </i>
+    <i t="grand" i="3">
+      <x/>
+    </i>
+    <i t="grand" i="4">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="13" hier="-1"/>
+  </pageFields>
+  <dataFields count="5">
+    <dataField name="Sum of Appt" fld="12" baseField="9" baseItem="0"/>
+    <dataField name="Average of Appts" fld="12" subtotal="average" baseField="9" baseItem="0"/>
+    <dataField name="Max of Appt Count" fld="12" subtotal="max" baseField="9" baseItem="0"/>
+    <dataField name="Min of Appt Counts" fld="12" subtotal="min" baseField="9" baseItem="0"/>
+    <dataField name="StdDev of Appt Count" fld="12" subtotal="stdDev" baseField="9" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2161,22 +2425,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -3960,99 +4224,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A1CBB3-AAD4-4D9E-9846-34A1E1AC494A}">
-  <dimension ref="A3:C20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FFD646-01A4-4BC8-8655-B94C3CCA43D8}">
+  <dimension ref="A2:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3">
+        <v>60</v>
+      </c>
+      <c r="J3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="str">
+        <f>LEFT(B4,6)</f>
+        <v>Tier 2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4">
+        <v>120</v>
+      </c>
+      <c r="J4">
+        <v>480</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4060,6 +4283,366 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A1CBB3-AAD4-4D9E-9846-34A1E1AC494A}">
+  <dimension ref="A3:C20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{665AD6E9-4B2D-4B07-8613-FB33375FE58E}">
+  <dimension ref="B1:Q9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C4" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N5" t="s">
+        <v>155</v>
+      </c>
+      <c r="O5" t="s">
+        <v>156</v>
+      </c>
+      <c r="P5" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="22">
+        <v>23</v>
+      </c>
+      <c r="D7" s="22">
+        <v>28</v>
+      </c>
+      <c r="E7" s="22">
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="F7" s="22">
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="G7" s="22">
+        <v>5</v>
+      </c>
+      <c r="H7" s="22">
+        <v>5</v>
+      </c>
+      <c r="I7" s="22">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22">
+        <v>2</v>
+      </c>
+      <c r="K7" s="22">
+        <v>1.7043362064926935</v>
+      </c>
+      <c r="L7" s="22">
+        <v>1.2692955176439846</v>
+      </c>
+      <c r="M7" s="22">
+        <v>51</v>
+      </c>
+      <c r="N7" s="22">
+        <v>3.1875</v>
+      </c>
+      <c r="O7" s="22">
+        <v>5</v>
+      </c>
+      <c r="P7" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="22">
+        <v>1.42448821218944</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="22">
+        <v>21</v>
+      </c>
+      <c r="D8" s="22">
+        <v>33</v>
+      </c>
+      <c r="E8" s="22">
+        <v>3</v>
+      </c>
+      <c r="F8" s="22">
+        <v>2.75</v>
+      </c>
+      <c r="G8" s="22">
+        <v>5</v>
+      </c>
+      <c r="H8" s="22">
+        <v>5</v>
+      </c>
+      <c r="I8" s="22">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22">
+        <v>1</v>
+      </c>
+      <c r="K8" s="22">
+        <v>1.7320508075688772</v>
+      </c>
+      <c r="L8" s="22">
+        <v>1.3568010505999362</v>
+      </c>
+      <c r="M8" s="22">
+        <v>54</v>
+      </c>
+      <c r="N8" s="22">
+        <v>2.8421052631578947</v>
+      </c>
+      <c r="O8" s="22">
+        <v>5</v>
+      </c>
+      <c r="P8" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="22">
+        <v>1.4629938062729388</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="22">
+        <v>44</v>
+      </c>
+      <c r="D9" s="22">
+        <v>61</v>
+      </c>
+      <c r="E9" s="22">
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="F9" s="22">
+        <v>2.9047619047619047</v>
+      </c>
+      <c r="G9" s="22">
+        <v>5</v>
+      </c>
+      <c r="H9" s="22">
+        <v>5</v>
+      </c>
+      <c r="I9" s="22">
+        <v>1</v>
+      </c>
+      <c r="J9" s="22">
+        <v>1</v>
+      </c>
+      <c r="K9" s="22">
+        <v>1.6574838603294899</v>
+      </c>
+      <c r="L9" s="22">
+        <v>1.3001831372834327</v>
+      </c>
+      <c r="M9" s="22">
+        <v>105</v>
+      </c>
+      <c r="N9" s="22">
+        <v>3</v>
+      </c>
+      <c r="O9" s="22">
+        <v>5</v>
+      </c>
+      <c r="P9" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="22">
+        <v>1.4348601079588785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B250BA-D121-4B99-9EB2-699DEC2E27E4}">
   <dimension ref="A1:U45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4082,27 +4665,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D2" s="5"/>
@@ -6715,7 +7298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1707823-7409-46EE-A6A7-19D5173EA8D7}">
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8322,7 +8905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B17465A-E33E-44CF-9672-9DAA4AFCA8CD}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
